--- a/capacity-mapping/data/CareSpace_Synthetic_DB.xlsx
+++ b/capacity-mapping/data/CareSpace_Synthetic_DB.xlsx
@@ -10,18 +10,20 @@
     <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Capacity by zone" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Inventory check" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="storage_zone" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="storage_unit_kind" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="agency" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="operator" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="storage_unit" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="capacity_snapshot" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="item" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="inventory" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="box_template" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="box_line" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="scan_session" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="scan_detection" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="What went out" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="storage_zone" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="storage_unit_kind" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="agency" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="operator" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="storage_unit" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="capacity_snapshot" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="item" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="inventory" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="box_template" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="box_line" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="distribution_event" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="scan_session" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="scan_detection" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -445,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A37"/>
+  <dimension ref="A1:A45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="82" customWidth="1" min="1" max="1"/>
@@ -653,26 +655,78 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>EMPTY TABLES</t>
+          <t>CAPACITY VS REALITY</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>scan_session and scan_detection are empty. Nothing has been scanned yet;</t>
+          <t>distribution_event records what actually went out the door. The gap</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>the vision model fills them. capacity_snapshot has one row per site per</t>
+          <t>against capacity has three different causes with three different owners:</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
+        <is>
+          <t>full and still turning people away means the site ran out of space, which</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>is the only one a storage product can fix. Room to spare means the food</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>never arrived or the families did not come. turned_away is the column</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>that tells them apart. See the 'What went out' sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>EMPTY TABLES</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>scan_session and scan_detection are empty. Nothing has been scanned yet;</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>the vision model fills them. capacity_snapshot has one row per site per</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>zone and no superseded rows, so there is no history in here yet.</t>
         </is>
@@ -684,6 +738,438 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>agency_id</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>zone_id</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>usable_cuft</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>measured_at</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>measured_by</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>superseded_by</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>cap_67253d8f</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>demo_agency</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>shelf_stable</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>73</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>scan</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>cap_a81e474c</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>demo_agency</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>refrigerated</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>scan</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cap_a60c1c7a</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>oceanside_crc</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>shelf_stable</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>153</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>scan</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cap_7ae1b2f0</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>oceanside_crc</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>refrigerated</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>12</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>scan</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cap_8e7676ae</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>apostolic_escondido</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>shelf_stable</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>104</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>scan</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cap_bba8becb</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>apostolic_escondido</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>refrigerated</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>scan</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cap_96817e90</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>all_saint_vista</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>shelf_stable</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>56</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>scan</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cap_4c631500</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>all_saint_vista</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>refrigerated</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>312</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>scan</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cap_c2e06984</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>vida_nueva_cv</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>shelf_stable</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>42</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>scan</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cap_6e7fd9af</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>vida_nueva_cv</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>refrigerated</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>18</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>scan</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cap_1f9c77e2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>aguilas_sd</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>shelf_stable</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>42</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>scan</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cap_4e9851b8</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>aguilas_sd</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>refrigerated</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1332,7 +1818,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>produce</t>
+          <t>refrigerated</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1370,7 +1856,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>produce</t>
+          <t>refrigerated</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1408,7 +1894,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>produce</t>
+          <t>refrigerated</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1446,7 +1932,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>produce</t>
+          <t>refrigerated</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1484,7 +1970,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>produce</t>
+          <t>refrigerated</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1522,7 +2008,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>produce</t>
+          <t>refrigerated</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1560,7 +2046,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>produce</t>
+          <t>refrigerated</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1585,13 +2071,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1637,12 +2123,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>inv_f338407a</t>
+          <t>inv_aeebdb0b</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>oceanside_crc</t>
+          <t>demo_agency</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1651,18 +2137,18 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>inv_731ebbf4</t>
+          <t>inv_d6b51908</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>oceanside_crc</t>
+          <t>demo_agency</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1671,18 +2157,18 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>inv_533554b5</t>
+          <t>inv_1703cda7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>oceanside_crc</t>
+          <t>demo_agency</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1691,18 +2177,18 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>inv_e59270e8</t>
+          <t>inv_944217cf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>oceanside_crc</t>
+          <t>demo_agency</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1711,38 +2197,38 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>inv_0cb385af</t>
+          <t>inv_34a489df</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>oceanside_crc</t>
+          <t>demo_agency</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cn_tuna</t>
+          <t>cn_blackbean</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>inv_c0813b9b</t>
+          <t>inv_f57be989</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>oceanside_crc</t>
+          <t>demo_agency</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1751,78 +2237,78 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>inv_f621e4a6</t>
+          <t>inv_39bd3a43</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>oceanside_crc</t>
+          <t>demo_agency</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>water</t>
+          <t>peanut_butter</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>inv_acb9b995</t>
+          <t>inv_cb3a79c1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>oceanside_crc</t>
+          <t>demo_agency</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>diapers_4</t>
+          <t>produce_box</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>inv_c9f4f5f2</t>
+          <t>inv_d313fee9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>oceanside_crc</t>
+          <t>demo_agency</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>produce_box</t>
+          <t>carrots</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>inv_a18a8a92</t>
+          <t>inv_da968221</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>oceanside_crc</t>
+          <t>demo_agency</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1831,18 +2317,18 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>inv_888213df</t>
+          <t>inv_a868ebf3</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>apostolic_escondido</t>
+          <t>oceanside_crc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1851,158 +2337,158 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>inv_e38aac76</t>
+          <t>inv_6be5f61d</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>apostolic_escondido</t>
+          <t>oceanside_crc</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>cn_corn</t>
+          <t>beans_pinto</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>inv_2817d24a</t>
+          <t>inv_387ed6f9</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>apostolic_escondido</t>
+          <t>oceanside_crc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>cn_tomato</t>
+          <t>pasta_spag</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>inv_764ac0ab</t>
+          <t>inv_ab276b25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>apostolic_escondido</t>
+          <t>oceanside_crc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>pasta_spag</t>
+          <t>cn_corn</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>inv_798e455e</t>
+          <t>inv_49cc9d48</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>apostolic_escondido</t>
+          <t>oceanside_crc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>cn_chicken</t>
+          <t>cn_tuna</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>inv_7115af86</t>
+          <t>inv_c239c36e</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>apostolic_escondido</t>
+          <t>oceanside_crc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>cereal</t>
+          <t>cn_chicken</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>inv_a6a40e89</t>
+          <t>inv_446eb1cc</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>apostolic_escondido</t>
+          <t>oceanside_crc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>diapers_4</t>
+          <t>water</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>inv_da4bf965</t>
+          <t>inv_1eac2ee0</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>apostolic_escondido</t>
+          <t>oceanside_crc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>pads</t>
+          <t>diapers_4</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>inv_f332d9cd</t>
+          <t>inv_51f8c5c9</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>apostolic_escondido</t>
+          <t>oceanside_crc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2011,43 +2497,43 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>inv_f7e7b414</t>
+          <t>inv_86232bd9</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>all_saint_vista</t>
+          <t>oceanside_crc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>rice_white</t>
+          <t>potatoes</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>inv_34bad0d9</t>
+          <t>inv_548e9451</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>all_saint_vista</t>
+          <t>apostolic_escondido</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>beans_pinto</t>
+          <t>rice_white</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2057,77 +2543,77 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>inv_00dd5d7f</t>
+          <t>inv_02dd8f41</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>all_saint_vista</t>
+          <t>apostolic_escondido</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>pasta_spag</t>
+          <t>cn_corn</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>inv_3cff0f1c</t>
+          <t>inv_7f456937</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>all_saint_vista</t>
+          <t>apostolic_escondido</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>cereal</t>
+          <t>cn_tomato</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>inv_6036c14e</t>
+          <t>inv_a1116484</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>all_saint_vista</t>
+          <t>apostolic_escondido</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>cn_blackbean</t>
+          <t>pasta_spag</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>inv_ca24da6a</t>
+          <t>inv_ec798172</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>all_saint_vista</t>
+          <t>apostolic_escondido</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>cn_corn</t>
+          <t>cn_chicken</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -2137,17 +2623,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>inv_9452c50b</t>
+          <t>inv_09feb65c</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>all_saint_vista</t>
+          <t>apostolic_escondido</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>cn_chicken</t>
+          <t>cereal</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -2157,67 +2643,67 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>inv_b3fa9236</t>
+          <t>inv_6a8fe629</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>all_saint_vista</t>
+          <t>apostolic_escondido</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>peanut_butter</t>
+          <t>diapers_4</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>inv_75c6660a</t>
+          <t>inv_69258c8d</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>all_saint_vista</t>
+          <t>apostolic_escondido</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>produce_box</t>
+          <t>pads</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>inv_09c292c0</t>
+          <t>inv_7486f57c</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>all_saint_vista</t>
+          <t>apostolic_escondido</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>carrots</t>
+          <t>produce_box</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>inv_2cc4cc7e</t>
+          <t>inv_39a53dd8</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2227,142 +2713,142 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>apples</t>
+          <t>rice_white</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>inv_5aee54e2</t>
+          <t>inv_2797fc80</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>vida_nueva_cv</t>
+          <t>all_saint_vista</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>rice_white</t>
+          <t>beans_pinto</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>inv_36925406</t>
+          <t>inv_306817f3</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>vida_nueva_cv</t>
+          <t>all_saint_vista</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>beans_pinto</t>
+          <t>pasta_spag</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>inv_b1bc9160</t>
+          <t>inv_84a04f7f</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>vida_nueva_cv</t>
+          <t>all_saint_vista</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>cn_blackbean</t>
+          <t>cereal</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>inv_0a055420</t>
+          <t>inv_769bf35a</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>vida_nueva_cv</t>
+          <t>all_saint_vista</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>cereal</t>
+          <t>cn_blackbean</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>inv_0d615511</t>
+          <t>inv_9d806afa</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>vida_nueva_cv</t>
+          <t>all_saint_vista</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>cn_chicken</t>
+          <t>cn_corn</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>inv_7df10b37</t>
+          <t>inv_9d66ed8c</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>vida_nueva_cv</t>
+          <t>all_saint_vista</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>pasta_spag</t>
+          <t>cn_chicken</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>inv_4dde9c85</t>
+          <t>inv_e1231265</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>vida_nueva_cv</t>
+          <t>all_saint_vista</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2377,52 +2863,52 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>inv_40ee026e</t>
+          <t>inv_8f2b94f1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>vida_nueva_cv</t>
+          <t>all_saint_vista</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>veg_oil</t>
+          <t>produce_box</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>inv_d004d8e9</t>
+          <t>inv_ac057141</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>vida_nueva_cv</t>
+          <t>all_saint_vista</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>produce_box</t>
+          <t>carrots</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>inv_d90691ea</t>
+          <t>inv_1128084d</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>vida_nueva_cv</t>
+          <t>all_saint_vista</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2431,18 +2917,18 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>inv_97c748f3</t>
+          <t>inv_b262a870</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>aguilas_sd</t>
+          <t>vida_nueva_cv</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2451,38 +2937,38 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>inv_a71d4bc2</t>
+          <t>inv_a81d6ba3</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>aguilas_sd</t>
+          <t>vida_nueva_cv</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>cn_corn</t>
+          <t>beans_pinto</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>inv_ceea7bae</t>
+          <t>inv_1057a97f</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>aguilas_sd</t>
+          <t>vida_nueva_cv</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2497,60 +2983,260 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>inv_e0526e55</t>
+          <t>inv_5841394c</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>aguilas_sd</t>
+          <t>vida_nueva_cv</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>cn_chicken</t>
+          <t>cereal</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>inv_4703217d</t>
+          <t>inv_db7a4473</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>aguilas_sd</t>
+          <t>vida_nueva_cv</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>pasta_spag</t>
+          <t>cn_chicken</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>inv_6b02e72b</t>
+          <t>inv_082160b8</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>vida_nueva_cv</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>pasta_spag</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>inv_88369e0e</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>vida_nueva_cv</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>peanut_butter</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>inv_455d1c82</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>vida_nueva_cv</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>veg_oil</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>inv_3ae8e0ad</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>vida_nueva_cv</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>produce_box</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>inv_3014f978</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>vida_nueva_cv</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>apples</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>inv_e550596e</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>aguilas_sd</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>rice_white</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>inv_e29956e2</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>aguilas_sd</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>cn_corn</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>inv_c2524c6a</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>aguilas_sd</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>cn_blackbean</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>inv_cd8c8829</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>aguilas_sd</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>cn_chicken</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>inv_fc72dee4</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>aguilas_sd</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>pasta_spag</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>inv_2b3f4563</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>aguilas_sd</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
         <is>
           <t>oats</t>
         </is>
       </c>
-      <c r="D47" t="n">
+      <c r="D57" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2559,7 +3245,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2630,20 +3316,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2676,7 +3362,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>bl_d22c0931</t>
+          <t>bl_a25ed8b5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2686,22 +3372,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rice_white</t>
+          <t>produce_box</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10 lb rice</t>
+          <t>1 produce box, 25-30 lb</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>bl_44f57fd0</t>
+          <t>bl_51e003b1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2711,7 +3397,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>beans_pinto</t>
+          <t>potatoes</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -2719,14 +3405,14 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2 lb dried beans</t>
+          <t>3 lb potatoes</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bl_a27b1aa1</t>
+          <t>bl_c8f8cb2a</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2736,22 +3422,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cn_blackbean</t>
+          <t>carrots</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.333</v>
+        <v>0.08</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4 cans black beans</t>
+          <t>2 lb carrots</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bl_de2bfe5f</t>
+          <t>bl_97dea21d</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2761,22 +3447,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cn_corn</t>
+          <t>onions</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.167</v>
+        <v>0.08</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2 cans corn</t>
+          <t>2 lb onions</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>bl_10093ba7</t>
+          <t>bl_328c431e</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2786,22 +3472,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cn_tomato</t>
+          <t>rice_white</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.167</v>
+        <v>0.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2 cans diced tomatoes</t>
+          <t>5 lb rice</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>bl_0e3680b2</t>
+          <t>bl_03809c7f</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2811,22 +3497,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cn_chicken</t>
+          <t>cn_blackbean</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.167</v>
+        <v>0.17</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2 cans chicken</t>
+          <t>2 cans black beans</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>bl_5918bf03</t>
+          <t>bl_532a2745</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2836,22 +3522,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cn_tuna</t>
+          <t>cn_chicken</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.083</v>
+        <v>0.17</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1 can tuna</t>
+          <t>2 cans chicken</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>bl_be15948b</t>
+          <t>bl_20d2813b</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2861,22 +3547,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>peanut_butter</t>
+          <t>cn_corn</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.083</v>
+        <v>0.08</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1 jar peanut butter</t>
+          <t>1 can corn</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bl_d998a21e</t>
+          <t>bl_dec9faaf</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2886,22 +3572,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>pasta_spag</t>
+          <t>peanut_butter</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.083</v>
+        <v>0.08</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1 lb pasta</t>
+          <t>1 jar peanut butter</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>bl_cc90fc06</t>
+          <t>bl_e9b5fa6f</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2911,90 +3597,15 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>cereal</t>
+          <t>pasta_spag</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.083</v>
+        <v>0.04</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1 box cereal</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>bl_7da6bef9</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>family_box</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>veg_oil</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>1 bottle cooking oil</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>bl_2dadc5ac</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>family_box</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>produce_box</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Half a mixed produce box</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>bl_3cd000c6</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>family_box</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>carrots</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2 lb carrots</t>
+          <t>1 lb pasta</t>
         </is>
       </c>
     </row>
@@ -3003,7 +3614,467 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>agency_id</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>distributed_on</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>boxes_out</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>people_served</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>turned_away</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>de_30d3b553</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>demo_agency</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E2" t="n">
+        <v>64</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>de_56689efe</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>demo_agency</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E3" t="n">
+        <v>72</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>de_c428c75a</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>demo_agency</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>15</v>
+      </c>
+      <c r="E4" t="n">
+        <v>60</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>de_f73fc37e</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>demo_agency</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>17</v>
+      </c>
+      <c r="E5" t="n">
+        <v>68</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>de_55b8c4b5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>oceanside_crc</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>32</v>
+      </c>
+      <c r="F6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ran out of boxes 50 minutes in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>de_b9f33c5e</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>oceanside_crc</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>32</v>
+      </c>
+      <c r="F7" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>de_e2c38d12</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>oceanside_crc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>32</v>
+      </c>
+      <c r="F8" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>de_c3a2e916</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>apostolic_escondido</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>28</v>
+      </c>
+      <c r="F9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>de_5c9fcb1c</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>apostolic_escondido</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>32</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>de_d9f98df4</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>all_saint_vista</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>103</v>
+      </c>
+      <c r="E11" t="n">
+        <v>412</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>de_7800b9a8</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>all_saint_vista</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>96</v>
+      </c>
+      <c r="E12" t="n">
+        <v>384</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>de_91afe55d</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>all_saint_vista</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>88</v>
+      </c>
+      <c r="E13" t="n">
+        <v>352</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>de_db0ffe5c</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>vida_nueva_cv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11</v>
+      </c>
+      <c r="E14" t="n">
+        <v>44</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>de_dd6cf584</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>vida_nueva_cv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12</v>
+      </c>
+      <c r="E15" t="n">
+        <v>48</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>de_dade6772</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>aguilas_sd</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>120</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Produce only, no complete boxes. Received and handed out the same morning.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3063,7 +4134,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3153,13 +4224,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
@@ -3242,13 +4313,13 @@
         <v>40.5</v>
       </c>
       <c r="G2" t="n">
-        <v>1.009</v>
+        <v>0.374</v>
       </c>
       <c r="H2" t="n">
-        <v>40</v>
+        <v>108</v>
       </c>
       <c r="I2" t="n">
-        <v>160</v>
+        <v>432</v>
       </c>
     </row>
     <row r="3">
@@ -3269,7 +4340,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Produce</t>
+          <t>Refrigerated Goods</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -3279,7 +4350,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.676</v>
+        <v>1.453</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -3316,13 +4387,13 @@
         <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>1.009</v>
+        <v>0.374</v>
       </c>
       <c r="H4" t="n">
-        <v>53</v>
+        <v>144</v>
       </c>
       <c r="I4" t="n">
-        <v>212</v>
+        <v>576</v>
       </c>
     </row>
     <row r="5">
@@ -3343,23 +4414,23 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Produce</t>
+          <t>Refrigerated Goods</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>120</v>
+        <v>480</v>
       </c>
       <c r="F5" t="n">
-        <v>78</v>
+        <v>312</v>
       </c>
       <c r="G5" t="n">
-        <v>0.676</v>
+        <v>1.453</v>
       </c>
       <c r="H5" t="n">
-        <v>115</v>
+        <v>214</v>
       </c>
       <c r="I5" t="n">
-        <v>460</v>
+        <v>856</v>
       </c>
     </row>
     <row r="6">
@@ -3390,13 +4461,13 @@
         <v>103.1</v>
       </c>
       <c r="G6" t="n">
-        <v>1.009</v>
+        <v>0.374</v>
       </c>
       <c r="H6" t="n">
-        <v>102</v>
+        <v>275</v>
       </c>
       <c r="I6" t="n">
-        <v>408</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="7">
@@ -3417,7 +4488,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Produce</t>
+          <t>Refrigerated Goods</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -3427,24 +4498,24 @@
         <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>0.676</v>
+        <v>1.453</v>
       </c>
       <c r="H7" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I7" t="n">
-        <v>68</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Iglesia Cristiana Vida Nueva</t>
+          <t>Demo Agency</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chula Vista</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3458,30 +4529,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c r="F8" t="n">
-        <v>40.5</v>
+        <v>71.8</v>
       </c>
       <c r="G8" t="n">
-        <v>1.009</v>
+        <v>0.374</v>
       </c>
       <c r="H8" t="n">
-        <v>40</v>
+        <v>192</v>
       </c>
       <c r="I8" t="n">
-        <v>160</v>
+        <v>768</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Iglesia Cristiana Vida Nueva</t>
+          <t>Demo Agency</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chula Vista</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3491,34 +4562,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Produce</t>
+          <t>Refrigerated Goods</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="F9" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G9" t="n">
-        <v>0.676</v>
+        <v>1.453</v>
       </c>
       <c r="H9" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="I9" t="n">
-        <v>104</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Oceanside Community Resource Center</t>
+          <t>Iglesia Cristiana Vida Nueva</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Oceanside</t>
+          <t>Chula Vista</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3532,56 +4603,130 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222</v>
+        <v>54</v>
       </c>
       <c r="F10" t="n">
-        <v>152.4</v>
+        <v>40.5</v>
       </c>
       <c r="G10" t="n">
-        <v>1.009</v>
+        <v>0.374</v>
       </c>
       <c r="H10" t="n">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="I10" t="n">
-        <v>600</v>
+        <v>432</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Iglesia Cristiana Vida Nueva</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Chula Vista</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Refrigerated Goods</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>24</v>
+      </c>
+      <c r="F11" t="n">
+        <v>18</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.453</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Oceanside Community Resource Center</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Oceanside</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Weekly</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Produce</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Shelf-stable</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222</v>
+      </c>
+      <c r="F12" t="n">
+        <v>152.4</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="H12" t="n">
+        <v>407</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Oceanside Community Resource Center</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Oceanside</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Refrigerated Goods</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
         <v>20</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F13" t="n">
         <v>12</v>
       </c>
-      <c r="G11" t="n">
-        <v>0.676</v>
-      </c>
-      <c r="H11" t="n">
-        <v>17</v>
-      </c>
-      <c r="I11" t="n">
-        <v>68</v>
+      <c r="G13" t="n">
+        <v>1.453</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -3595,11 +4740,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
@@ -3681,7 +4826,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Produce</t>
+          <t>Refrigerated Goods</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -3739,7 +4884,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Produce</t>
+          <t>Refrigerated Goods</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -3752,7 +4897,7 @@
         <v>37.8</v>
       </c>
       <c r="F5" t="n">
-        <v>78</v>
+        <v>312</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -3797,7 +4942,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Produce</t>
+          <t>Refrigerated Goods</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -3821,7 +4966,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Iglesia Cristiana Vida Nueva</t>
+          <t>Demo Agency</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3830,16 +4975,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="D8" t="n">
-        <v>767</v>
+        <v>1549</v>
       </c>
       <c r="E8" t="n">
-        <v>26.9</v>
+        <v>48.1</v>
       </c>
       <c r="F8" t="n">
-        <v>40.5</v>
+        <v>71.8</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -3850,25 +4995,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Iglesia Cristiana Vida Nueva</t>
+          <t>Demo Agency</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Produce</t>
+          <t>Refrigerated Goods</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D9" t="n">
-        <v>276</v>
+        <v>484</v>
       </c>
       <c r="E9" t="n">
-        <v>11.9</v>
+        <v>20.3</v>
       </c>
       <c r="F9" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -3879,7 +5024,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Oceanside Community Resource Center</t>
+          <t>Iglesia Cristiana Vida Nueva</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3888,16 +5033,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>156</v>
+        <v>44</v>
       </c>
       <c r="D10" t="n">
-        <v>3011</v>
+        <v>767</v>
       </c>
       <c r="E10" t="n">
-        <v>103.3</v>
+        <v>26.9</v>
       </c>
       <c r="F10" t="n">
-        <v>152.4</v>
+        <v>40.5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -3908,27 +5053,85 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>Iglesia Cristiana Vida Nueva</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Refrigerated Goods</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="n">
+        <v>276</v>
+      </c>
+      <c r="E11" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="F11" t="n">
+        <v>18</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>fits</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Oceanside Community Resource Center</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Produce</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Shelf-stable</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>156</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3011</v>
+      </c>
+      <c r="E12" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>152.4</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>fits</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Oceanside Community Resource Center</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Refrigerated Goods</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
         <v>6</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D13" t="n">
         <v>165</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E13" t="n">
         <v>7</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F13" t="n">
         <v>12</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>fits</t>
         </is>
@@ -3945,11 +5148,471 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Agency</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Cadence</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Boxes out</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>People served</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Turned away</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Aguilas del Poderoso Dios</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>120</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Produce only, no complete boxes. Received and handed out the same morning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>All Saint Episcopal Church</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>103</v>
+      </c>
+      <c r="E3" t="n">
+        <v>412</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>All Saint Episcopal Church</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>96</v>
+      </c>
+      <c r="E4" t="n">
+        <v>384</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>All Saint Episcopal Church</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>88</v>
+      </c>
+      <c r="E5" t="n">
+        <v>352</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Apostolic Assembly Church</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>28</v>
+      </c>
+      <c r="F6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Apostolic Assembly Church</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>32</v>
+      </c>
+      <c r="F7" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Demo Agency</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>16</v>
+      </c>
+      <c r="E8" t="n">
+        <v>64</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Demo Agency</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>18</v>
+      </c>
+      <c r="E9" t="n">
+        <v>72</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Demo Agency</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>15</v>
+      </c>
+      <c r="E10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Demo Agency</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>17</v>
+      </c>
+      <c r="E11" t="n">
+        <v>68</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Iglesia Cristiana Vida Nueva</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" t="n">
+        <v>44</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Iglesia Cristiana Vida Nueva</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12</v>
+      </c>
+      <c r="E13" t="n">
+        <v>48</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Oceanside Community Resource Center</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>8</v>
+      </c>
+      <c r="E14" t="n">
+        <v>32</v>
+      </c>
+      <c r="F14" t="n">
+        <v>40</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Ran out of boxes 50 minutes in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Oceanside Community Resource Center</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" t="n">
+        <v>32</v>
+      </c>
+      <c r="F15" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Oceanside Community Resource Center</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>8</v>
+      </c>
+      <c r="E16" t="n">
+        <v>32</v>
+      </c>
+      <c r="F16" t="n">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -4006,12 +5669,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>produce</t>
+          <t>refrigerated</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Produce</t>
+          <t>Refrigerated Goods</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -4029,7 +5692,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4195,7 +5858,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>produce</t>
+          <t>refrigerated</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -4221,7 +5884,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>produce</t>
+          <t>refrigerated</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -4247,7 +5910,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>produce</t>
+          <t>refrigerated</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -4265,13 +5928,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4291,7 +5954,8 @@
     <col width="25" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4382,6 +6046,11 @@
       </c>
       <c r="R1" s="2" t="inlineStr">
         <is>
+          <t>is_demo</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
           <t>provenance</t>
         </is>
       </c>
@@ -4389,32 +6058,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>oceanside_crc</t>
+          <t>demo_agency</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Oceanside Community Resource Center</t>
+          <t>Demo Agency</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>605 South Coast Highway</t>
+          <t>100 Example Street</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Oceanside</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>92054</t>
+          <t>92101</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Food To Nonprofit</t>
+          <t>Neighborhood Distribution</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -4429,7 +6098,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -4439,12 +6108,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>9:00 am</t>
+          <t>10:00 am</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1:00 pm</t>
+          <t>2:00 pm</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -4454,7 +6123,7 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -4462,7 +6131,10 @@
       <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>synthetic</t>
         </is>
@@ -4471,61 +6143,66 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>apostolic_escondido</t>
+          <t>oceanside_crc</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Apostolic Assembly Church</t>
+          <t>Oceanside Community Resource Center</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1717 East Lincoln Avenue</t>
+          <t>605 South Coast Highway</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Escondido</t>
+          <t>Oceanside</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>92027</t>
+          <t>92054</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Neighborhood Distribution</t>
+          <t>Food To Nonprofit</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neighborhood Produce (25-30lb)</t>
+          <t>Nonperishable Dry Goods + Produce</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Open to All</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Weekly</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>9:30 am</t>
+          <t>9:00 am</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>10:30 am</t>
+          <t>1:00 pm</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
@@ -4534,12 +6211,15 @@
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>synthetic</t>
         </is>
@@ -4548,42 +6228,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>all_saint_vista</t>
+          <t>apostolic_escondido</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>All Saint Episcopal Church</t>
+          <t>Apostolic Assembly Church</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>651 Eucalyptus Avenue</t>
+          <t>1717 East Lincoln Avenue</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Vista</t>
+          <t>Escondido</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>92084</t>
+          <t>92027</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Food To Nonprofit</t>
+          <t>Neighborhood Distribution</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nonperishable Dry Goods + Produce</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Open to All</t>
+          <t>Neighborhood Produce (25-30lb)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -4598,22 +6273,22 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>11:00 am</t>
+          <t>9:30 am</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>12:00 pm</t>
+          <t>10:30 am</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -4621,7 +6296,10 @@
       <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>synthetic</t>
         </is>
@@ -4630,32 +6308,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>vida_nueva_cv</t>
+          <t>all_saint_vista</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Iglesia Cristiana Vida Nueva</t>
+          <t>All Saint Episcopal Church</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1240 Third Avenue</t>
+          <t>651 Eucalyptus Avenue</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Chula Vista</t>
+          <t>Vista</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>91911</t>
+          <t>92084</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Neighborhood Distribution</t>
+          <t>Food To Nonprofit</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -4670,26 +6348,26 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4:00 pm</t>
+          <t>11:00 am</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>6:00 pm</t>
+          <t>12:00 pm</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -4698,12 +6376,15 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>synthetic</t>
         </is>
@@ -4712,27 +6393,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>aguilas_sd</t>
+          <t>vida_nueva_cv</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Aguilas del Poderoso Dios</t>
+          <t>Iglesia Cristiana Vida Nueva</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5901 Rancho Hills Drive</t>
+          <t>1240 Third Avenue</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Chula Vista</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>92139</t>
+          <t>91911</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -4742,7 +6423,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neighborhood Produce (25-30lb)</t>
+          <t>Nonperishable Dry Goods + Produce</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -4752,29 +6433,29 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>Weekly</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>10:00 am</t>
+          <t>4:00 pm</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>until food runs out</t>
+          <t>6:00 pm</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -4785,7 +6466,95 @@
       <c r="Q6" t="n">
         <v>0</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>synthetic</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>aguilas_sd</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Aguilas del Poderoso Dios</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>5901 Rancho Hills Drive</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>San Diego</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>92139</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Neighborhood Distribution</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Neighborhood Produce (25-30lb)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Open to All</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>10:00 am</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>until food runs out</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>synthetic</t>
         </is>
@@ -4796,7 +6565,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4921,13 +6690,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5021,12 +6790,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>su_3c54f1b9</t>
+          <t>su_2714d8e4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>oceanside_crc</t>
+          <t>demo_agency</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -5056,7 +6825,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="L2" t="n">
         <v>1</v>
@@ -5075,12 +6844,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>su_558d9e33</t>
+          <t>su_245ca5ec</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>oceanside_crc</t>
+          <t>demo_agency</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -5090,19 +6859,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>pallet_rack</t>
+          <t>wire_shelving</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pallet rack, bay 2</t>
+          <t>Shelving, back room</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -5110,7 +6879,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -5129,12 +6898,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>su_e7beb4bd</t>
+          <t>su_d6a02145</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>oceanside_crc</t>
+          <t>demo_agency</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5144,19 +6913,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>pallet_rack</t>
+          <t>wire_shelving</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pallet rack, bay 3</t>
+          <t>Shelving, front room</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -5164,7 +6933,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -5183,34 +6952,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>su_86540ace</t>
+          <t>su_5d089fdc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>oceanside_crc</t>
+          <t>demo_agency</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>shelf_stable</t>
+          <t>refrigerated</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>floor_stack</t>
+          <t>reach_in_cooler</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Floor staging, dock</t>
+          <t>Reach-in cooler</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -5218,7 +6987,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.68</v>
+        <v>0.91</v>
       </c>
       <c r="L5" t="n">
         <v>1</v>
@@ -5237,17 +7006,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>su_a93695b1</t>
+          <t>su_16962420</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>oceanside_crc</t>
+          <t>demo_agency</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>produce</t>
+          <t>refrigerated</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -5257,7 +7026,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Break room fridge</t>
+          <t>Kitchen fridge</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -5272,7 +7041,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
@@ -5291,12 +7060,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>su_aba784e5</t>
+          <t>su_8a5e406b</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>apostolic_escondido</t>
+          <t>oceanside_crc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5326,7 +7095,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
@@ -5345,12 +7114,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>su_4c7323e1</t>
+          <t>su_9e28ab1e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>apostolic_escondido</t>
+          <t>oceanside_crc</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -5380,7 +7149,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="L8" t="n">
         <v>1</v>
@@ -5399,12 +7168,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>su_63d7ac69</t>
+          <t>su_b42485ca</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>apostolic_escondido</t>
+          <t>oceanside_crc</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5414,19 +7183,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>wire_shelving</t>
+          <t>pallet_rack</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shelving, supply closet</t>
+          <t>Pallet rack, bay 3</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="G9" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -5434,7 +7203,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.77</v>
+        <v>0.9</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
@@ -5453,31 +7222,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>su_77e035f7</t>
+          <t>su_06ed4dcb</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>apostolic_escondido</t>
+          <t>oceanside_crc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>produce</t>
+          <t>shelf_stable</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>residential_fridge</t>
+          <t>floor_stack</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kitchen fridge</t>
+          <t>Floor staging, dock</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G10" t="n">
         <v>0.6</v>
@@ -5488,7 +7257,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.85</v>
+        <v>0.68</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
@@ -5507,34 +7276,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>su_30e7145a</t>
+          <t>su_09909ebb</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>all_saint_vista</t>
+          <t>oceanside_crc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>shelf_stable</t>
+          <t>refrigerated</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>wire_shelving</t>
+          <t>residential_fridge</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shelving, fellowship hall north wall</t>
+          <t>Break room fridge</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G11" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -5542,7 +7311,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.88</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
@@ -5561,12 +7330,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>su_c1b2f6d5</t>
+          <t>su_fde45845</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>all_saint_vista</t>
+          <t>apostolic_escondido</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -5576,19 +7345,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>wire_shelving</t>
+          <t>pallet_rack</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shelving, fellowship hall south wall</t>
+          <t>Pallet rack, bay 1</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="G12" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -5596,7 +7365,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
@@ -5615,12 +7384,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>su_00ed9232</t>
+          <t>su_e0a16213</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>all_saint_vista</t>
+          <t>apostolic_escondido</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5630,19 +7399,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>wire_shelving</t>
+          <t>pallet_rack</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Shelving, hallway</t>
+          <t>Pallet rack, bay 2</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="G13" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -5650,7 +7419,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="L13" t="n">
         <v>1</v>
@@ -5669,12 +7438,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>su_f8368b07</t>
+          <t>su_f1a50aa8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>all_saint_vista</t>
+          <t>apostolic_escondido</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -5689,7 +7458,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shelving, kitchen pantry</t>
+          <t>Shelving, supply closet</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -5704,7 +7473,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="L14" t="n">
         <v>1</v>
@@ -5723,34 +7492,34 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>su_d3ca5d1f</t>
+          <t>su_b8a94f85</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>all_saint_vista</t>
+          <t>apostolic_escondido</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>produce</t>
+          <t>refrigerated</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>walk_in_cooler</t>
+          <t>residential_fridge</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Walk-in cooler, kitchen</t>
+          <t>Kitchen fridge</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>120</v>
+        <v>20</v>
       </c>
       <c r="G15" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -5758,7 +7527,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="L15" t="n">
         <v>1</v>
@@ -5777,12 +7546,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>su_c99912ce</t>
+          <t>su_21ef50a7</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>vida_nueva_cv</t>
+          <t>all_saint_vista</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -5797,7 +7566,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shelving, pantry room</t>
+          <t>Shelving, fellowship hall north wall</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -5812,7 +7581,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="L16" t="n">
         <v>1</v>
@@ -5831,12 +7600,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>su_bbcc930f</t>
+          <t>su_5965cfa5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>vida_nueva_cv</t>
+          <t>all_saint_vista</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5851,7 +7620,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shelving, pantry room</t>
+          <t>Shelving, fellowship hall south wall</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -5866,7 +7635,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="L17" t="n">
         <v>1</v>
@@ -5885,12 +7654,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>su_c42891fe</t>
+          <t>su_5b78f8cb</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>vida_nueva_cv</t>
+          <t>all_saint_vista</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5905,7 +7674,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shelving, pantry room</t>
+          <t>Shelving, hallway</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -5920,7 +7689,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.88</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L18" t="n">
         <v>1</v>
@@ -5939,31 +7708,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>su_3283c644</t>
+          <t>su_8e21cdd8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>vida_nueva_cv</t>
+          <t>all_saint_vista</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>produce</t>
+          <t>shelf_stable</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>reach_in_cooler</t>
+          <t>wire_shelving</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Reach-in cooler</t>
+          <t>Shelving, kitchen pantry</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="G19" t="n">
         <v>0.75</v>
@@ -5974,7 +7743,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>0.79</v>
       </c>
       <c r="L19" t="n">
         <v>1</v>
@@ -5993,34 +7762,34 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>su_255fe04e</t>
+          <t>su_1c757752</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>aguilas_sd</t>
+          <t>all_saint_vista</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>shelf_stable</t>
+          <t>refrigerated</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>wire_shelving</t>
+          <t>walk_in_cooler</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shelving, storage room</t>
+          <t>Walk-in cooler, kitchen</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>18</v>
+        <v>480</v>
       </c>
       <c r="G20" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -6028,7 +7797,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="L20" t="n">
         <v>1</v>
@@ -6047,12 +7816,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>su_94a86e56</t>
+          <t>su_1d13e479</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>aguilas_sd</t>
+          <t>vida_nueva_cv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -6067,7 +7836,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shelving, storage room</t>
+          <t>Shelving, pantry room</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -6082,7 +7851,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="L21" t="n">
         <v>1</v>
@@ -6101,12 +7870,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>su_e43b4f63</t>
+          <t>su_99b96630</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>aguilas_sd</t>
+          <t>vida_nueva_cv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -6121,7 +7890,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shelving, back office</t>
+          <t>Shelving, pantry room</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -6136,7 +7905,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.72</v>
+        <v>0.93</v>
       </c>
       <c r="L22" t="n">
         <v>1</v>
@@ -6152,373 +7921,271 @@
         </is>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>agency_id</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>zone_id</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>usable_cuft</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>reason</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>measured_at</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>measured_by</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>superseded_by</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>cap_cbc3115f</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>oceanside_crc</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>su_b8a4d6cd</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>vida_nueva_cv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>shelf_stable</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>152.4</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>wire_shelving</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Shelving, pantry room</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>18</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t>scan</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I23" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>cap_df7ad87c</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>oceanside_crc</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>produce</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>12</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>su_fcacfb5b</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>vida_nueva_cv</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>refrigerated</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>reach_in_cooler</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Reach-in cooler</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>24</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>scan</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I24" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cap_e7c05616</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>apostolic_escondido</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>su_7190be53</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>aguilas_sd</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>shelf_stable</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>103.1</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>wire_shelving</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Shelving, storage room</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>18</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>scan</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I25" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cap_dd1016ad</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>apostolic_escondido</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>produce</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>12</v>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>su_064bd6ef</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>aguilas_sd</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>shelf_stable</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>wire_shelving</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Shelving, storage room</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>18</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t>scan</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I26" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>cap_7559f4aa</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>all_saint_vista</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>su_fa1d9595</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>aguilas_sd</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>shelf_stable</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>54</v>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>wire_shelving</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Shelving, back office</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>18</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t>scan</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I27" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>cap_41bb62d2</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>all_saint_vista</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>produce</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>78</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>scan</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>cap_988ad20c</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>vida_nueva_cv</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>shelf_stable</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>scan</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>cap_4246a9bd</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>vida_nueva_cv</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>produce</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>18</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>scan</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>cap_f1c5bf5a</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>aguilas_sd</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>shelf_stable</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>scan</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>cap_72546f60</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>aguilas_sd</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>produce</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
